--- a/ig/DM-SIDOBA/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="938">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00.000+00:00</t>
+    <t>2026-05-05T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1480,7 +1480,10 @@
     <t>236</t>
   </si>
   <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant. Remarque : Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>
@@ -5829,17 +5832,19 @@
       <c r="C207" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="D207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>489</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5848,10 +5853,10 @@
         <v>87</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5860,10 +5865,10 @@
         <v>87</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5872,10 +5877,10 @@
         <v>87</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5884,10 +5889,10 @@
         <v>87</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5896,10 +5901,10 @@
         <v>87</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5908,10 +5913,10 @@
         <v>87</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5920,10 +5925,10 @@
         <v>87</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5932,10 +5937,10 @@
         <v>87</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5944,10 +5949,10 @@
         <v>87</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5956,10 +5961,10 @@
         <v>87</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5968,10 +5973,10 @@
         <v>87</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5980,10 +5985,10 @@
         <v>87</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5992,10 +5997,10 @@
         <v>87</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6004,10 +6009,10 @@
         <v>87</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6016,10 +6021,10 @@
         <v>87</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6028,10 +6033,10 @@
         <v>87</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6040,10 +6045,10 @@
         <v>87</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6052,10 +6057,10 @@
         <v>87</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6064,10 +6069,10 @@
         <v>87</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -6076,10 +6081,10 @@
         <v>87</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6088,10 +6093,10 @@
         <v>87</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6100,10 +6105,10 @@
         <v>87</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6112,10 +6117,10 @@
         <v>87</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6124,10 +6129,10 @@
         <v>87</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -6136,10 +6141,10 @@
         <v>87</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6148,10 +6153,10 @@
         <v>87</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -6160,10 +6165,10 @@
         <v>87</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -6172,10 +6177,10 @@
         <v>87</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -6184,10 +6189,10 @@
         <v>87</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -6196,10 +6201,10 @@
         <v>87</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -6208,10 +6213,10 @@
         <v>87</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6220,10 +6225,10 @@
         <v>87</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -6232,10 +6237,10 @@
         <v>87</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6244,10 +6249,10 @@
         <v>87</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -6256,10 +6261,10 @@
         <v>87</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6268,10 +6273,10 @@
         <v>87</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -6280,10 +6285,10 @@
         <v>87</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6292,10 +6297,10 @@
         <v>87</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -6304,10 +6309,10 @@
         <v>87</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6316,10 +6321,10 @@
         <v>87</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6328,10 +6333,10 @@
         <v>87</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6340,10 +6345,10 @@
         <v>87</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6352,10 +6357,10 @@
         <v>87</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6364,10 +6369,10 @@
         <v>87</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6376,10 +6381,10 @@
         <v>87</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6388,10 +6393,10 @@
         <v>87</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6400,10 +6405,10 @@
         <v>87</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6412,10 +6417,10 @@
         <v>87</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6424,10 +6429,10 @@
         <v>87</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6436,10 +6441,10 @@
         <v>87</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6448,10 +6453,10 @@
         <v>87</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6460,10 +6465,10 @@
         <v>87</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6472,10 +6477,10 @@
         <v>87</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6484,10 +6489,10 @@
         <v>87</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6496,10 +6501,10 @@
         <v>87</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6508,10 +6513,10 @@
         <v>87</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6520,10 +6525,10 @@
         <v>87</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6532,10 +6537,10 @@
         <v>87</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6544,10 +6549,10 @@
         <v>87</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -6556,10 +6561,10 @@
         <v>87</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -6568,10 +6573,10 @@
         <v>87</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -6580,10 +6585,10 @@
         <v>87</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -6592,10 +6597,10 @@
         <v>87</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -6604,10 +6609,10 @@
         <v>87</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -6616,10 +6621,10 @@
         <v>87</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -6628,10 +6633,10 @@
         <v>87</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -6640,7 +6645,7 @@
         <v>87</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C275" t="s" s="2">
         <v>201</v>
@@ -6652,10 +6657,10 @@
         <v>87</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -6664,10 +6669,10 @@
         <v>87</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -6676,10 +6681,10 @@
         <v>87</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -6688,10 +6693,10 @@
         <v>87</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -6700,10 +6705,10 @@
         <v>87</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -6712,10 +6717,10 @@
         <v>87</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -6724,10 +6729,10 @@
         <v>87</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6736,10 +6741,10 @@
         <v>87</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6748,10 +6753,10 @@
         <v>87</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6760,10 +6765,10 @@
         <v>87</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6772,10 +6777,10 @@
         <v>87</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6784,10 +6789,10 @@
         <v>87</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6796,10 +6801,10 @@
         <v>87</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6808,10 +6813,10 @@
         <v>87</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6820,10 +6825,10 @@
         <v>87</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6832,10 +6837,10 @@
         <v>87</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6844,10 +6849,10 @@
         <v>87</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6856,10 +6861,10 @@
         <v>87</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6868,10 +6873,10 @@
         <v>87</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6880,10 +6885,10 @@
         <v>87</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6892,10 +6897,10 @@
         <v>87</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6904,10 +6909,10 @@
         <v>87</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6916,10 +6921,10 @@
         <v>87</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6928,10 +6933,10 @@
         <v>87</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6940,10 +6945,10 @@
         <v>87</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6952,10 +6957,10 @@
         <v>87</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6964,10 +6969,10 @@
         <v>87</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6976,10 +6981,10 @@
         <v>87</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6988,10 +6993,10 @@
         <v>87</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -7000,10 +7005,10 @@
         <v>87</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -7012,10 +7017,10 @@
         <v>87</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7024,10 +7029,10 @@
         <v>87</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7036,10 +7041,10 @@
         <v>87</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7048,10 +7053,10 @@
         <v>87</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7060,10 +7065,10 @@
         <v>87</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7072,10 +7077,10 @@
         <v>87</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7084,10 +7089,10 @@
         <v>87</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7096,10 +7101,10 @@
         <v>87</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7108,10 +7113,10 @@
         <v>87</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7120,10 +7125,10 @@
         <v>87</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7132,10 +7137,10 @@
         <v>87</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7144,10 +7149,10 @@
         <v>87</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7156,10 +7161,10 @@
         <v>87</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7168,10 +7173,10 @@
         <v>87</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7180,10 +7185,10 @@
         <v>87</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7192,10 +7197,10 @@
         <v>87</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7204,10 +7209,10 @@
         <v>87</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7216,10 +7221,10 @@
         <v>87</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7228,10 +7233,10 @@
         <v>87</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7240,10 +7245,10 @@
         <v>87</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7252,10 +7257,10 @@
         <v>87</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7264,10 +7269,10 @@
         <v>87</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7276,10 +7281,10 @@
         <v>87</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7288,10 +7293,10 @@
         <v>87</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7300,10 +7305,10 @@
         <v>87</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7312,10 +7317,10 @@
         <v>87</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7324,10 +7329,10 @@
         <v>87</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7336,10 +7341,10 @@
         <v>87</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7348,10 +7353,10 @@
         <v>87</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7360,10 +7365,10 @@
         <v>87</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7372,10 +7377,10 @@
         <v>87</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7384,10 +7389,10 @@
         <v>87</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7396,10 +7401,10 @@
         <v>87</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7408,10 +7413,10 @@
         <v>87</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7420,10 +7425,10 @@
         <v>87</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7432,10 +7437,10 @@
         <v>87</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7444,10 +7449,10 @@
         <v>87</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7456,10 +7461,10 @@
         <v>87</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7468,10 +7473,10 @@
         <v>87</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7480,10 +7485,10 @@
         <v>87</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7492,10 +7497,10 @@
         <v>87</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7504,10 +7509,10 @@
         <v>87</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7516,10 +7521,10 @@
         <v>87</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7528,10 +7533,10 @@
         <v>87</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7540,10 +7545,10 @@
         <v>87</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7552,10 +7557,10 @@
         <v>87</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7564,10 +7569,10 @@
         <v>87</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7576,10 +7581,10 @@
         <v>87</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7588,10 +7593,10 @@
         <v>87</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7600,10 +7605,10 @@
         <v>87</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7612,10 +7617,10 @@
         <v>87</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7624,10 +7629,10 @@
         <v>87</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7636,10 +7641,10 @@
         <v>87</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7648,10 +7653,10 @@
         <v>87</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7660,10 +7665,10 @@
         <v>87</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7672,10 +7677,10 @@
         <v>87</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7684,10 +7689,10 @@
         <v>87</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7696,10 +7701,10 @@
         <v>87</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7708,10 +7713,10 @@
         <v>87</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7720,10 +7725,10 @@
         <v>87</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7732,10 +7737,10 @@
         <v>87</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7744,10 +7749,10 @@
         <v>87</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7756,10 +7761,10 @@
         <v>87</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7768,10 +7773,10 @@
         <v>87</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7780,10 +7785,10 @@
         <v>87</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7792,10 +7797,10 @@
         <v>87</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7804,10 +7809,10 @@
         <v>87</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7816,10 +7821,10 @@
         <v>87</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7828,10 +7833,10 @@
         <v>87</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7840,10 +7845,10 @@
         <v>87</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7852,10 +7857,10 @@
         <v>87</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7864,7 +7869,7 @@
         <v>87</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>173</v>
@@ -7876,10 +7881,10 @@
         <v>87</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7888,13 +7893,13 @@
         <v>87</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="380">
@@ -7902,7 +7907,7 @@
         <v>87</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>177</v>
@@ -7914,10 +7919,10 @@
         <v>87</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7926,10 +7931,10 @@
         <v>87</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7938,10 +7943,10 @@
         <v>87</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7950,10 +7955,10 @@
         <v>87</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7962,10 +7967,10 @@
         <v>87</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7974,10 +7979,10 @@
         <v>87</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7986,10 +7991,10 @@
         <v>87</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7998,10 +8003,10 @@
         <v>87</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8010,7 +8015,7 @@
         <v>87</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>211</v>
@@ -8022,13 +8027,13 @@
         <v>87</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="391">
@@ -8036,10 +8041,10 @@
         <v>87</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8048,10 +8053,10 @@
         <v>87</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8060,10 +8065,10 @@
         <v>87</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8072,10 +8077,10 @@
         <v>87</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8084,10 +8089,10 @@
         <v>87</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8096,10 +8101,10 @@
         <v>87</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8108,10 +8113,10 @@
         <v>87</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8120,10 +8125,10 @@
         <v>87</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8132,10 +8137,10 @@
         <v>87</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8144,10 +8149,10 @@
         <v>87</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8156,10 +8161,10 @@
         <v>87</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8168,10 +8173,10 @@
         <v>87</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8180,10 +8185,10 @@
         <v>87</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8192,10 +8197,10 @@
         <v>87</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8204,10 +8209,10 @@
         <v>87</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8216,10 +8221,10 @@
         <v>87</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8228,10 +8233,10 @@
         <v>87</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8240,10 +8245,10 @@
         <v>87</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8252,10 +8257,10 @@
         <v>87</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8264,10 +8269,10 @@
         <v>87</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8276,10 +8281,10 @@
         <v>87</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8288,10 +8293,10 @@
         <v>87</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8300,10 +8305,10 @@
         <v>87</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8312,10 +8317,10 @@
         <v>87</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8324,10 +8329,10 @@
         <v>87</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8336,10 +8341,10 @@
         <v>87</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8348,13 +8353,13 @@
         <v>87</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="418">
@@ -8362,13 +8367,13 @@
         <v>87</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D418" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="419">
@@ -8376,10 +8381,10 @@
         <v>87</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8388,10 +8393,10 @@
         <v>87</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8400,10 +8405,10 @@
         <v>87</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8412,10 +8417,10 @@
         <v>87</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8424,10 +8429,10 @@
         <v>87</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8436,10 +8441,10 @@
         <v>87</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8448,13 +8453,13 @@
         <v>87</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="426">
@@ -8462,13 +8467,13 @@
         <v>87</v>
       </c>
       <c r="B426" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="C426" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="D426" t="s" s="2">
         <v>926</v>
-      </c>
-      <c r="C426" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="D426" t="s" s="2">
-        <v>925</v>
       </c>
     </row>
     <row r="427">
@@ -8476,13 +8481,13 @@
         <v>87</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="428">
@@ -8490,10 +8495,10 @@
         <v>87</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8502,13 +8507,13 @@
         <v>87</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D429" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="430">
@@ -8516,13 +8521,13 @@
         <v>87</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D430" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SIDOBA/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="937">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>429</t>
+    <t>428</t>
   </si>
   <si>
     <t>Code</t>
@@ -326,9 +326,6 @@
   </si>
   <si>
     <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
   </si>
   <si>
     <t>1100</t>
@@ -3345,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3466,7 +3463,7 @@
         <v>104</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -3475,10 +3472,10 @@
         <v>87</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -3487,10 +3484,10 @@
         <v>87</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3499,10 +3496,10 @@
         <v>87</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -3514,7 +3511,7 @@
         <v>111</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -3523,10 +3520,10 @@
         <v>87</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -3535,10 +3532,10 @@
         <v>87</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -3550,7 +3547,7 @@
         <v>116</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -3559,10 +3556,10 @@
         <v>87</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -3571,10 +3568,10 @@
         <v>87</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -3583,10 +3580,10 @@
         <v>87</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -3595,10 +3592,10 @@
         <v>87</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3607,10 +3604,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -3619,10 +3616,10 @@
         <v>87</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -3634,7 +3631,7 @@
         <v>129</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -3643,10 +3640,10 @@
         <v>87</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -3655,10 +3652,10 @@
         <v>87</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -3667,10 +3664,10 @@
         <v>87</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -3682,7 +3679,7 @@
         <v>136</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -3691,10 +3688,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -3703,10 +3700,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -3715,10 +3712,10 @@
         <v>87</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -3727,10 +3724,10 @@
         <v>87</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -3739,10 +3736,10 @@
         <v>87</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -3751,10 +3748,10 @@
         <v>87</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D34" s="2"/>
     </row>
@@ -3763,10 +3760,10 @@
         <v>87</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -3775,10 +3772,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -3787,10 +3784,10 @@
         <v>87</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -3799,10 +3796,10 @@
         <v>87</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -3811,10 +3808,10 @@
         <v>87</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -3823,10 +3820,10 @@
         <v>87</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -3835,10 +3832,10 @@
         <v>87</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D41" s="2"/>
     </row>
@@ -3847,10 +3844,10 @@
         <v>87</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -3859,10 +3856,10 @@
         <v>87</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -3871,10 +3868,10 @@
         <v>87</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -3886,7 +3883,7 @@
         <v>169</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="D45" s="2"/>
     </row>
@@ -3895,10 +3892,10 @@
         <v>87</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -3907,10 +3904,10 @@
         <v>87</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -3919,10 +3916,10 @@
         <v>87</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -3931,10 +3928,10 @@
         <v>87</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -3943,10 +3940,10 @@
         <v>87</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -3955,10 +3952,10 @@
         <v>87</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -3967,10 +3964,10 @@
         <v>87</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -3979,10 +3976,10 @@
         <v>87</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -3991,10 +3988,10 @@
         <v>87</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -4003,10 +4000,10 @@
         <v>87</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -4018,7 +4015,7 @@
         <v>190</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -4030,7 +4027,7 @@
         <v>191</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -4039,10 +4036,10 @@
         <v>87</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -4051,10 +4048,10 @@
         <v>87</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -4063,10 +4060,10 @@
         <v>87</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -4075,10 +4072,10 @@
         <v>87</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -4087,10 +4084,10 @@
         <v>87</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -4099,10 +4096,10 @@
         <v>87</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -4111,10 +4108,10 @@
         <v>87</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -4123,10 +4120,10 @@
         <v>87</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -4135,10 +4132,10 @@
         <v>87</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -4147,10 +4144,10 @@
         <v>87</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -4159,10 +4156,10 @@
         <v>87</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -4171,10 +4168,10 @@
         <v>87</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -4183,10 +4180,10 @@
         <v>87</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -4195,10 +4192,10 @@
         <v>87</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -4207,10 +4204,10 @@
         <v>87</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -4219,10 +4216,10 @@
         <v>87</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -4231,10 +4228,10 @@
         <v>87</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -4243,10 +4240,10 @@
         <v>87</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -4255,10 +4252,10 @@
         <v>87</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -4267,10 +4264,10 @@
         <v>87</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -4279,10 +4276,10 @@
         <v>87</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -4291,10 +4288,10 @@
         <v>87</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -4303,10 +4300,10 @@
         <v>87</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -4315,10 +4312,10 @@
         <v>87</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -4327,10 +4324,10 @@
         <v>87</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -4339,10 +4336,10 @@
         <v>87</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -4351,10 +4348,10 @@
         <v>87</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -4363,10 +4360,10 @@
         <v>87</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -4375,10 +4372,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -4387,10 +4384,10 @@
         <v>87</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -4399,10 +4396,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -4411,10 +4408,10 @@
         <v>87</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -4423,10 +4420,10 @@
         <v>87</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -4435,10 +4432,10 @@
         <v>87</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -4447,10 +4444,10 @@
         <v>87</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -4459,10 +4456,10 @@
         <v>87</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -4471,10 +4468,10 @@
         <v>87</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -4483,10 +4480,10 @@
         <v>87</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -4495,10 +4492,10 @@
         <v>87</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -4507,10 +4504,10 @@
         <v>87</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -4519,10 +4516,10 @@
         <v>87</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -4531,10 +4528,10 @@
         <v>87</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -4543,10 +4540,10 @@
         <v>87</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -4555,10 +4552,10 @@
         <v>87</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -4567,10 +4564,10 @@
         <v>87</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -4579,10 +4576,10 @@
         <v>87</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>283</v>
+        <v>130</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -4594,7 +4591,7 @@
         <v>284</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>131</v>
+        <v>285</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -4603,10 +4600,10 @@
         <v>87</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -4615,10 +4612,10 @@
         <v>87</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>288</v>
+        <v>132</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -4630,7 +4627,7 @@
         <v>289</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -4642,7 +4639,7 @@
         <v>290</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -4651,10 +4648,10 @@
         <v>87</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -4663,10 +4660,10 @@
         <v>87</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -4675,10 +4672,10 @@
         <v>87</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -4687,10 +4684,10 @@
         <v>87</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -4699,10 +4696,10 @@
         <v>87</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -4711,10 +4708,10 @@
         <v>87</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -4723,10 +4720,10 @@
         <v>87</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -4735,10 +4732,10 @@
         <v>87</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -4747,10 +4744,10 @@
         <v>87</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -4759,10 +4756,10 @@
         <v>87</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -4771,10 +4768,10 @@
         <v>87</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -4783,10 +4780,10 @@
         <v>87</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -4795,10 +4792,10 @@
         <v>87</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -4807,10 +4804,10 @@
         <v>87</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -4819,10 +4816,10 @@
         <v>87</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -4831,10 +4828,10 @@
         <v>87</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -4843,10 +4840,10 @@
         <v>87</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -4855,10 +4852,10 @@
         <v>87</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -4867,10 +4864,10 @@
         <v>87</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -4879,10 +4876,10 @@
         <v>87</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -4891,10 +4888,10 @@
         <v>87</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -4903,10 +4900,10 @@
         <v>87</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -4915,10 +4912,10 @@
         <v>87</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -4927,10 +4924,10 @@
         <v>87</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -4939,10 +4936,10 @@
         <v>87</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -4951,10 +4948,10 @@
         <v>87</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -4963,10 +4960,10 @@
         <v>87</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -4975,10 +4972,10 @@
         <v>87</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -4987,10 +4984,10 @@
         <v>87</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -4999,10 +4996,10 @@
         <v>87</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -5011,10 +5008,10 @@
         <v>87</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -5023,10 +5020,10 @@
         <v>87</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -5035,10 +5032,10 @@
         <v>87</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -5047,10 +5044,10 @@
         <v>87</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -5059,10 +5056,10 @@
         <v>87</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -5071,10 +5068,10 @@
         <v>87</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -5083,10 +5080,10 @@
         <v>87</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -5095,10 +5092,10 @@
         <v>87</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -5107,10 +5104,10 @@
         <v>87</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -5119,10 +5116,10 @@
         <v>87</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -5131,10 +5128,10 @@
         <v>87</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -5143,10 +5140,10 @@
         <v>87</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -5155,10 +5152,10 @@
         <v>87</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -5167,10 +5164,10 @@
         <v>87</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -5179,10 +5176,10 @@
         <v>87</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -5191,10 +5188,10 @@
         <v>87</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -5203,10 +5200,10 @@
         <v>87</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -5215,10 +5212,10 @@
         <v>87</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -5227,10 +5224,10 @@
         <v>87</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -5239,10 +5236,10 @@
         <v>87</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -5251,10 +5248,10 @@
         <v>87</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -5263,10 +5260,10 @@
         <v>87</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -5275,10 +5272,10 @@
         <v>87</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -5287,10 +5284,10 @@
         <v>87</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5299,10 +5296,10 @@
         <v>87</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5311,10 +5308,10 @@
         <v>87</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5323,10 +5320,10 @@
         <v>87</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -5335,10 +5332,10 @@
         <v>87</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5347,10 +5344,10 @@
         <v>87</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5359,10 +5356,10 @@
         <v>87</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5371,10 +5368,10 @@
         <v>87</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -5383,10 +5380,10 @@
         <v>87</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5395,10 +5392,10 @@
         <v>87</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -5407,10 +5404,10 @@
         <v>87</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5419,10 +5416,10 @@
         <v>87</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5431,10 +5428,10 @@
         <v>87</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5443,10 +5440,10 @@
         <v>87</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5455,10 +5452,10 @@
         <v>87</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5467,10 +5464,10 @@
         <v>87</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5479,10 +5476,10 @@
         <v>87</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5491,10 +5488,10 @@
         <v>87</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -5503,10 +5500,10 @@
         <v>87</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -5515,10 +5512,10 @@
         <v>87</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5527,10 +5524,10 @@
         <v>87</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -5539,10 +5536,10 @@
         <v>87</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5551,10 +5548,10 @@
         <v>87</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -5563,10 +5560,10 @@
         <v>87</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -5575,10 +5572,10 @@
         <v>87</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -5587,10 +5584,10 @@
         <v>87</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -5599,10 +5596,10 @@
         <v>87</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -5611,10 +5608,10 @@
         <v>87</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -5623,10 +5620,10 @@
         <v>87</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -5635,10 +5632,10 @@
         <v>87</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -5647,10 +5644,10 @@
         <v>87</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -5659,10 +5656,10 @@
         <v>87</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -5671,10 +5668,10 @@
         <v>87</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -5683,10 +5680,10 @@
         <v>87</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -5695,10 +5692,10 @@
         <v>87</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -5707,10 +5704,10 @@
         <v>87</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -5719,10 +5716,10 @@
         <v>87</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5731,10 +5728,10 @@
         <v>87</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5743,10 +5740,10 @@
         <v>87</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5755,10 +5752,10 @@
         <v>87</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5767,10 +5764,10 @@
         <v>87</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5779,10 +5776,10 @@
         <v>87</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5791,10 +5788,10 @@
         <v>87</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -5803,10 +5800,10 @@
         <v>87</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -5815,36 +5812,36 @@
         <v>87</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="D206" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="D206" t="s" s="2">
+        <v>488</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="D207" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5853,10 +5850,10 @@
         <v>87</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5865,10 +5862,10 @@
         <v>87</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5877,10 +5874,10 @@
         <v>87</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5889,10 +5886,10 @@
         <v>87</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5901,10 +5898,10 @@
         <v>87</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5913,10 +5910,10 @@
         <v>87</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5925,10 +5922,10 @@
         <v>87</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5937,10 +5934,10 @@
         <v>87</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5949,10 +5946,10 @@
         <v>87</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5961,10 +5958,10 @@
         <v>87</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5973,10 +5970,10 @@
         <v>87</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5985,10 +5982,10 @@
         <v>87</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5997,10 +5994,10 @@
         <v>87</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6009,10 +6006,10 @@
         <v>87</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6021,10 +6018,10 @@
         <v>87</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6033,10 +6030,10 @@
         <v>87</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6045,10 +6042,10 @@
         <v>87</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6057,10 +6054,10 @@
         <v>87</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6069,10 +6066,10 @@
         <v>87</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -6081,10 +6078,10 @@
         <v>87</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6093,10 +6090,10 @@
         <v>87</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6105,10 +6102,10 @@
         <v>87</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6117,10 +6114,10 @@
         <v>87</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6129,10 +6126,10 @@
         <v>87</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -6141,10 +6138,10 @@
         <v>87</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6153,10 +6150,10 @@
         <v>87</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -6165,10 +6162,10 @@
         <v>87</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -6177,10 +6174,10 @@
         <v>87</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -6189,10 +6186,10 @@
         <v>87</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -6201,10 +6198,10 @@
         <v>87</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -6213,10 +6210,10 @@
         <v>87</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6225,10 +6222,10 @@
         <v>87</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -6237,10 +6234,10 @@
         <v>87</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6249,10 +6246,10 @@
         <v>87</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -6261,10 +6258,10 @@
         <v>87</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6273,10 +6270,10 @@
         <v>87</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -6285,10 +6282,10 @@
         <v>87</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6297,10 +6294,10 @@
         <v>87</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -6309,10 +6306,10 @@
         <v>87</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6321,10 +6318,10 @@
         <v>87</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6333,10 +6330,10 @@
         <v>87</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6345,10 +6342,10 @@
         <v>87</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6357,10 +6354,10 @@
         <v>87</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6369,10 +6366,10 @@
         <v>87</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6381,10 +6378,10 @@
         <v>87</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6393,10 +6390,10 @@
         <v>87</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6405,10 +6402,10 @@
         <v>87</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6417,10 +6414,10 @@
         <v>87</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6429,10 +6426,10 @@
         <v>87</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6441,10 +6438,10 @@
         <v>87</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6453,10 +6450,10 @@
         <v>87</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6465,10 +6462,10 @@
         <v>87</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6477,10 +6474,10 @@
         <v>87</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6489,10 +6486,10 @@
         <v>87</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6501,10 +6498,10 @@
         <v>87</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6513,10 +6510,10 @@
         <v>87</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6525,10 +6522,10 @@
         <v>87</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6537,10 +6534,10 @@
         <v>87</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6549,10 +6546,10 @@
         <v>87</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -6561,10 +6558,10 @@
         <v>87</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -6573,10 +6570,10 @@
         <v>87</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -6585,10 +6582,10 @@
         <v>87</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -6597,10 +6594,10 @@
         <v>87</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -6609,10 +6606,10 @@
         <v>87</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -6621,10 +6618,10 @@
         <v>87</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -6633,10 +6630,10 @@
         <v>87</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>623</v>
+        <v>200</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -6648,7 +6645,7 @@
         <v>624</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>201</v>
+        <v>625</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -6657,10 +6654,10 @@
         <v>87</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -6669,10 +6666,10 @@
         <v>87</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -6681,10 +6678,10 @@
         <v>87</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -6693,10 +6690,10 @@
         <v>87</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -6705,10 +6702,10 @@
         <v>87</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -6717,10 +6714,10 @@
         <v>87</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -6729,10 +6726,10 @@
         <v>87</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6741,10 +6738,10 @@
         <v>87</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6753,10 +6750,10 @@
         <v>87</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6765,10 +6762,10 @@
         <v>87</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6777,10 +6774,10 @@
         <v>87</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6789,10 +6786,10 @@
         <v>87</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6801,10 +6798,10 @@
         <v>87</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6813,10 +6810,10 @@
         <v>87</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6825,10 +6822,10 @@
         <v>87</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6837,10 +6834,10 @@
         <v>87</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6849,10 +6846,10 @@
         <v>87</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6861,10 +6858,10 @@
         <v>87</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6873,10 +6870,10 @@
         <v>87</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6885,10 +6882,10 @@
         <v>87</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6897,10 +6894,10 @@
         <v>87</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6909,10 +6906,10 @@
         <v>87</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6921,10 +6918,10 @@
         <v>87</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6933,10 +6930,10 @@
         <v>87</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6945,10 +6942,10 @@
         <v>87</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6957,10 +6954,10 @@
         <v>87</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6969,10 +6966,10 @@
         <v>87</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6981,10 +6978,10 @@
         <v>87</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6993,10 +6990,10 @@
         <v>87</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -7005,10 +7002,10 @@
         <v>87</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -7017,10 +7014,10 @@
         <v>87</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7029,10 +7026,10 @@
         <v>87</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7041,10 +7038,10 @@
         <v>87</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7053,10 +7050,10 @@
         <v>87</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7065,10 +7062,10 @@
         <v>87</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7077,10 +7074,10 @@
         <v>87</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7089,10 +7086,10 @@
         <v>87</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7101,10 +7098,10 @@
         <v>87</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7113,10 +7110,10 @@
         <v>87</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7125,10 +7122,10 @@
         <v>87</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7137,10 +7134,10 @@
         <v>87</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7149,10 +7146,10 @@
         <v>87</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7161,10 +7158,10 @@
         <v>87</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7173,10 +7170,10 @@
         <v>87</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7185,10 +7182,10 @@
         <v>87</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7197,10 +7194,10 @@
         <v>87</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7209,10 +7206,10 @@
         <v>87</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7221,10 +7218,10 @@
         <v>87</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7233,10 +7230,10 @@
         <v>87</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7245,10 +7242,10 @@
         <v>87</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7257,10 +7254,10 @@
         <v>87</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7269,10 +7266,10 @@
         <v>87</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7281,10 +7278,10 @@
         <v>87</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7293,10 +7290,10 @@
         <v>87</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7305,10 +7302,10 @@
         <v>87</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7317,10 +7314,10 @@
         <v>87</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7329,10 +7326,10 @@
         <v>87</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7341,10 +7338,10 @@
         <v>87</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7353,10 +7350,10 @@
         <v>87</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7365,10 +7362,10 @@
         <v>87</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7377,10 +7374,10 @@
         <v>87</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7389,10 +7386,10 @@
         <v>87</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7401,10 +7398,10 @@
         <v>87</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7413,10 +7410,10 @@
         <v>87</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7425,10 +7422,10 @@
         <v>87</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7437,10 +7434,10 @@
         <v>87</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7449,10 +7446,10 @@
         <v>87</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7461,10 +7458,10 @@
         <v>87</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7473,10 +7470,10 @@
         <v>87</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7485,10 +7482,10 @@
         <v>87</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7497,10 +7494,10 @@
         <v>87</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7509,10 +7506,10 @@
         <v>87</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7521,10 +7518,10 @@
         <v>87</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7533,10 +7530,10 @@
         <v>87</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7545,10 +7542,10 @@
         <v>87</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7557,10 +7554,10 @@
         <v>87</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7569,10 +7566,10 @@
         <v>87</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7581,10 +7578,10 @@
         <v>87</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7593,10 +7590,10 @@
         <v>87</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7605,10 +7602,10 @@
         <v>87</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7617,10 +7614,10 @@
         <v>87</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7629,10 +7626,10 @@
         <v>87</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7641,10 +7638,10 @@
         <v>87</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7653,10 +7650,10 @@
         <v>87</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7665,10 +7662,10 @@
         <v>87</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7677,10 +7674,10 @@
         <v>87</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7689,10 +7686,10 @@
         <v>87</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7701,10 +7698,10 @@
         <v>87</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7713,10 +7710,10 @@
         <v>87</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7725,10 +7722,10 @@
         <v>87</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7737,10 +7734,10 @@
         <v>87</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7749,10 +7746,10 @@
         <v>87</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7761,10 +7758,10 @@
         <v>87</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7773,10 +7770,10 @@
         <v>87</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7785,10 +7782,10 @@
         <v>87</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7797,10 +7794,10 @@
         <v>87</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7809,10 +7806,10 @@
         <v>87</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7821,10 +7818,10 @@
         <v>87</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7833,10 +7830,10 @@
         <v>87</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7845,10 +7842,10 @@
         <v>87</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7857,10 +7854,10 @@
         <v>87</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>826</v>
+        <v>172</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7872,7 +7869,7 @@
         <v>827</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>173</v>
+        <v>828</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7881,26 +7878,26 @@
         <v>87</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="D378" s="2"/>
+        <v>830</v>
+      </c>
+      <c r="D378" t="s" s="2">
+        <v>831</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="D379" t="s" s="2">
-        <v>832</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="D379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
@@ -7910,7 +7907,7 @@
         <v>833</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>177</v>
+        <v>834</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -7919,10 +7916,10 @@
         <v>87</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7931,10 +7928,10 @@
         <v>87</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7943,10 +7940,10 @@
         <v>87</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7955,10 +7952,10 @@
         <v>87</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7967,10 +7964,10 @@
         <v>87</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7979,10 +7976,10 @@
         <v>87</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7991,10 +7988,10 @@
         <v>87</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -8003,10 +8000,10 @@
         <v>87</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>849</v>
+        <v>210</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8018,33 +8015,33 @@
         <v>850</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="D389" s="2"/>
+        <v>851</v>
+      </c>
+      <c r="D389" t="s" s="2">
+        <v>852</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="D390" t="s" s="2">
-        <v>853</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8053,10 +8050,10 @@
         <v>87</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8065,10 +8062,10 @@
         <v>87</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8077,10 +8074,10 @@
         <v>87</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8089,10 +8086,10 @@
         <v>87</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8101,10 +8098,10 @@
         <v>87</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8113,10 +8110,10 @@
         <v>87</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8125,10 +8122,10 @@
         <v>87</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8137,10 +8134,10 @@
         <v>87</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8149,10 +8146,10 @@
         <v>87</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8161,10 +8158,10 @@
         <v>87</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8173,10 +8170,10 @@
         <v>87</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8185,10 +8182,10 @@
         <v>87</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8197,10 +8194,10 @@
         <v>87</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8209,10 +8206,10 @@
         <v>87</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8221,10 +8218,10 @@
         <v>87</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8233,10 +8230,10 @@
         <v>87</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8245,10 +8242,10 @@
         <v>87</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8257,10 +8254,10 @@
         <v>87</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8269,10 +8266,10 @@
         <v>87</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8281,10 +8278,10 @@
         <v>87</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8293,10 +8290,10 @@
         <v>87</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8305,10 +8302,10 @@
         <v>87</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8317,10 +8314,10 @@
         <v>87</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8329,10 +8326,10 @@
         <v>87</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8341,25 +8338,27 @@
         <v>87</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="D416" s="2"/>
+        <v>906</v>
+      </c>
+      <c r="D416" t="s" s="2">
+        <v>907</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="418">
@@ -8367,24 +8366,22 @@
         <v>87</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="D418" t="s" s="2">
-        <v>911</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8393,10 +8390,10 @@
         <v>87</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8405,10 +8402,10 @@
         <v>87</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8417,10 +8414,10 @@
         <v>87</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8429,10 +8426,10 @@
         <v>87</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8441,25 +8438,27 @@
         <v>87</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="D424" s="2"/>
+        <v>924</v>
+      </c>
+      <c r="D424" t="s" s="2">
+        <v>925</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C425" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>925</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>926</v>
       </c>
     </row>
     <row r="426">
@@ -8467,13 +8466,13 @@
         <v>87</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="427">
@@ -8481,53 +8480,39 @@
         <v>87</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="D427" t="s" s="2">
-        <v>926</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="D427" s="2"/>
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>932</v>
-      </c>
-      <c r="D428" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="D428" t="s" s="2">
+        <v>934</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D429" t="s" s="2">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="B430" t="s" s="2">
-        <v>936</v>
-      </c>
-      <c r="C430" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="D430" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
   </sheetData>
